--- a/public/documents/pieces-reponse-1/R1-alcool-cuisine-encadrement.xlsx
+++ b/public/documents/pieces-reponse-1/R1-alcool-cuisine-encadrement.xlsx
@@ -1017,7 +1017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1393,28 +1393,28 @@
         </is>
       </c>
       <c r="C12" s="5" t="n">
-        <v>980</v>
+        <v>280</v>
       </c>
       <c r="D12" s="5" t="n">
         <v>20</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>890</v>
+        <v>190</v>
       </c>
       <c r="F12" s="5" t="n">
         <v>558</v>
       </c>
       <c r="G12" s="8" t="n">
-        <v>1.59</v>
+        <v>0.34</v>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>6.38</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>oui</t>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="I12" s="10" t="inlineStr">
+        <is>
+          <t>non : plafonnee aux achats</t>
         </is>
       </c>
     </row>
@@ -1466,6 +1466,20 @@
       <c r="A16" t="inlineStr">
         <is>
           <t>Volume disponible : colonne du service (p. 65 a 67) pour le Calvados, le vin jaune, le porto et le macvin ; achats factures FCBS pour les six autres.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Marc de Bourgogne : 280 cl, soit les 4 bouteilles du code article 550252 (Jacoulot 45 degres). Les 980 cl du cumul du dossier etaient un total de famille : ils y ajoutaient 700 cl de marc du Jura Tissot 50 degres (code 520096, 10 bouteilles), qui est un autre produit, vendu au verre.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire : 1 750 cl, soit les 25 bouteilles du code article 591050, la ligne du 15/03/2024 (facture n. 508974) portant une designation tronquee que le rapprochement par libelle avait perdue.</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2430,10 +2444,10 @@
         </is>
       </c>
       <c r="C28" s="5" t="n">
-        <v>630</v>
+        <v>70</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>630</v>
+        <v>70</v>
       </c>
       <c r="E28" s="5" t="n">
         <v>8</v>
@@ -2451,7 +2465,7 @@
         <v>530</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>92</v>
+        <v>-468</v>
       </c>
     </row>
     <row r="29">
@@ -2466,10 +2480,10 @@
         </is>
       </c>
       <c r="C29" s="5" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="D29" s="5" t="n">
-        <v>280</v>
+        <v>140</v>
       </c>
       <c r="E29" s="5" t="n">
         <v>4</v>
@@ -2487,7 +2501,7 @@
         <v>28</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>248</v>
+        <v>108</v>
       </c>
     </row>
     <row r="30">
@@ -2632,6 +2646,20 @@
       </c>
       <c r="J33" s="5" t="n">
         <v>494</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Marc de Bourgogne : achats du seul code article 550252 (Jacoulot 45 degres), 70 + 140 + 70 cl. Le marc du Jura Tissot 50 degres (code 520096, 700 cl) est un produit distinct, vendu au verre, et ne figure pas dans ce bilan. Le reste negatif de l exercice 1 est precisement le motif du plafonnement retenu a la feuille 4 : nous ramenons la demande a 210 cl sur les trois exercices.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Liqueur de Poire : achats du code article 591050, 140 + 840 + 770 cl, soit 25 bouteilles de 70 cl.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -2645,7 +2673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2927,20 +2955,20 @@
         <v>5.58</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>9.800000000000001</v>
+        <v>2.8</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>5.58</v>
+        <v>2.1</v>
       </c>
       <c r="E12" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>5.58</v>
+        <v>2.1</v>
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>aucun retranchement identifie ; 14 bouteilles de marc facturees sur 3 exercices</t>
+          <t>aucun retranchement identifie ; 4 bouteilles de marc de Bourgogne Jacoulot 45 degres facturees sur 3 exercices, soit 280 cl (code article 550252) ; demande plafonnee a 210 cl, volume sorti du stock, et non aux 5,58 L calcules. Le marc du Jura Tissot 50 degres (code 520096, 10 bouteilles, 700 cl) est un autre produit, vendu au verre</t>
         </is>
       </c>
     </row>
@@ -2981,16 +3009,16 @@
         <v>794.62</v>
       </c>
       <c r="C14" s="14" t="n">
-        <v>1724.9</v>
+        <v>1717.9</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>744.61</v>
+        <v>741.13</v>
       </c>
       <c r="E14" s="14" t="n">
         <v>811.63</v>
       </c>
       <c r="F14" s="14" t="n">
-        <v>173.38</v>
+        <v>169.9</v>
       </c>
       <c r="G14" s="13" t="inlineStr"/>
     </row>
@@ -3004,7 +3032,21 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sensibilite du plafond : achats factures FCBS 744.6 L ; colonne « volume disponible » du service 747.1 L ; le plus faible des deux 743.6 L.</t>
+          <t>Sensibilite du plafond : achats factures FCBS 741.1 L ; colonne « volume disponible » du service 743.6 L ; le plus faible des deux 740.1 L.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>La colonne « cuisine calculee » n est jamais modifiee par un plafonnement : elle reste le produit du nombre de plats par la dose. Le Calvados y garde 119,1 L en face de 73,0 L retenus, le marc de Bourgogne 5,58 L en face de 2,10 L retenus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Le plafonnement joue exercice par exercice, sauf pour le marc de Bourgogne, plafonne sur les trois exercices pris ensemble aux 210 cl sortis du stock (280 cl factures moins la bouteille inventoriee au 31/03/2025), faute de savoir lequel des deux marcs achetes entre dans le baba.</t>
         </is>
       </c>
     </row>
